--- a/AiArtTinder.xlsx
+++ b/AiArtTinder.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TinderAR\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projekte\AIArtExtendedPlus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD18AE4D-A39D-492D-81CA-06ADF17A689B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF59A0D-3C46-4C10-ABC6-1561139414E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24555" yWindow="435" windowWidth="32760" windowHeight="14940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23295" yWindow="495" windowWidth="32760" windowHeight="14940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
